--- a/assets/toolkits/organizational-impact-score.xlsx
+++ b/assets/toolkits/organizational-impact-score.xlsx
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Need help?</t>
   </si>
   <si>
-    <t xml:space="preserve">Book a free 30 minute call: calendly.com/productadvisory/30min | info@productadvisory.co | (727) 386-6815</t>
+    <t xml:space="preserve">Book a free 30 minute call: productadvisory.co/book | info@productadvisory.co | (727) 386-6815</t>
   </si>
   <si>
     <t xml:space="preserve">Terms</t>
